--- a/Confluence demo — screen copy.xlsx
+++ b/Confluence demo — screen copy.xlsx
@@ -9,10 +9,9 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Screen copy" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Limits" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Screen copy'!$A$1:$K$161</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Screen copy'!$A$1:$K$151</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -68,10 +67,6 @@
     <font>
       <color rgb="0097A6BD"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="5">
@@ -123,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -160,18 +155,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -634,10 +617,10 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>HARD  — going over changes the layout: text overflows, or the buttons below it move. Please stay inside it.</t>
+          <t>HARD  — going over changes the layout: text overflows, or the buttons below it move.</t>
         </is>
       </c>
     </row>
@@ -651,7 +634,7 @@
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Column I says what happens on that specific field if you go past.</t>
+          <t>Column I says what happens on that specific field.</t>
         </is>
       </c>
     </row>
@@ -685,31 +668,48 @@
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Still open</t>
+          <t>What changed on 8 September</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Case studies are placeholders. They are written to the right shape and length so the screen can be built, but no client detail in them is real. They carry a "Placeholder content" badge on screen. Replace them and tell us to drop the badge.</t>
+          <t>The stats card that sat between the intro and the framework was removed, so the three proof points it carried — the market size figure, the top-200-clients figure and the case study count — are no longer anywhere in the demo. Those rows have gone from this sheet with it.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>The "400+ client case studies" figure needs Nitin to confirm it. See the note on that row.</t>
+          <t>The guidebook QR screen was removed earlier, for the same reason: nothing to hand over.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr"/>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Word counts are a guide. Characters are what the layout measures, so trust column F over column G.</t>
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>Still open</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="45" customHeight="1">
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Case studies are placeholders. They are written to the right shape and length so the screen can be built, but no client detail in them is real. They carry a "Placeholder content" badge on screen. Replace them and tell us to drop the badge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Word counts are a guide. Characters are what the layout measures, so trust column F over G.</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -863,10 +863,10 @@
         <v/>
       </c>
       <c r="F3" s="10" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G3" s="10" t="n">
-        <v>120</v>
+        <v>55</v>
       </c>
       <c r="H3" s="10" t="inlineStr">
         <is>
@@ -875,7 +875,7 @@
       </c>
       <c r="I3" s="11" t="inlineStr">
         <is>
-          <t>Sits on one line today. Past ~52 characters it wraps to two, which is still fine.</t>
+          <t>Sits on one line today. Past ~52 characters it wraps to two, still fine.</t>
         </is>
       </c>
       <c r="J3" s="11" t="inlineStr"/>
@@ -907,10 +907,10 @@
         <v/>
       </c>
       <c r="F4" s="10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G4" s="10" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="H4" s="10" t="inlineStr">
         <is>
@@ -976,7 +976,7 @@
     <row r="6" ht="46" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>02 Framework</t>
         </is>
       </c>
       <c r="B6" s="7" t="inlineStr">
@@ -1002,12 +1002,12 @@
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I6" s="11" t="inlineStr">
         <is>
-          <t>Baked into the hexagon artwork, not live text. Any change needs the artwork remade.</t>
+          <t>Live text in the middle of the hexagon. Longer just sets wider.</t>
         </is>
       </c>
       <c r="J6" s="11" t="inlineStr"/>
@@ -1020,7 +1020,7 @@
     <row r="7" ht="46" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>02 Framework</t>
         </is>
       </c>
       <c r="B7" s="7" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I7" s="11" t="inlineStr">
         <is>
-          <t>Baked into the hexagon artwork, not live text. Any change needs the artwork remade.</t>
+          <t>Live text in the middle of the hexagon. Longer just sets wider.</t>
         </is>
       </c>
       <c r="J7" s="11" t="inlineStr"/>
@@ -1064,17 +1064,17 @@
     <row r="8" ht="46" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 — Data for AI</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Headline L1</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Six value pools.</t>
+          <t>INSIGHT</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -1083,10 +1083,10 @@
         <v/>
       </c>
       <c r="F8" s="10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="10" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="H8" s="10" t="inlineStr">
         <is>
@@ -1095,30 +1095,30 @@
       </c>
       <c r="I8" s="11" t="inlineStr">
         <is>
-          <t>Two lines by design, one per row. Longer just sets wider.</t>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
         </is>
       </c>
       <c r="J8" s="11" t="inlineStr"/>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>BRAND.headline[0]</t>
+          <t>POOLS[0].verb</t>
         </is>
       </c>
     </row>
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 — Data for AI</t>
         </is>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Headline L2</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Deeply interconnected.</t>
+          <t>Data for AI</t>
         </is>
       </c>
       <c r="D9" s="9" t="n"/>
@@ -1127,42 +1127,42 @@
         <v/>
       </c>
       <c r="F9" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G9" s="10" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="H9" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I9" s="11" t="inlineStr">
         <is>
-          <t>Two lines by design, one per row. Longer just sets wider.</t>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
         </is>
       </c>
       <c r="J9" s="11" t="inlineStr"/>
       <c r="K9" s="12" t="inlineStr">
         <is>
-          <t>BRAND.headline[1]</t>
+          <t>POOLS[0].title</t>
         </is>
       </c>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 — Data for AI</t>
         </is>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Sub-headline</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>A structured path to orchestrate data, technology and operations at scale. Beyond experimentation, into the enterprise.</t>
+          <t>Raw enterprise data becomes a trusted, model-ready asset, so analytics and prediction run on one version of the truth. We build the platforms that get it there, and use fingerprinting and synthetic data to fill the gaps privacy leaves behind. What comes out the other side is decisions made in real time, not reports written after the fact.</t>
         </is>
       </c>
       <c r="D10" s="9" t="n"/>
@@ -1171,42 +1171,42 @@
         <v/>
       </c>
       <c r="F10" s="10" t="n">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="G10" s="10" t="n">
-        <v>130</v>
+        <v>340</v>
       </c>
       <c r="H10" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I10" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: two lines today at 119 characters. A third line is safe.</t>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
         </is>
       </c>
       <c r="J10" s="11" t="inlineStr"/>
       <c r="K10" s="12" t="inlineStr">
         <is>
-          <t>BRAND.subhead</t>
+          <t>POOLS[0].description</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Button</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Explore the framework</t>
+          <t>Global insurer</t>
         </is>
       </c>
       <c r="D11" s="9" t="n"/>
@@ -1215,10 +1215,10 @@
         <v/>
       </c>
       <c r="F11" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" s="10" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
@@ -1227,30 +1227,34 @@
       </c>
       <c r="I11" s="11" t="inlineStr">
         <is>
-          <t>Button grows to fit the label.</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
-          <t>BRAND.continueCta</t>
+          <t>POOLS[0].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="12" ht="46" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Stat 1 figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>$300–400B</t>
+          <t>Claims data unified for model readiness</t>
         </is>
       </c>
       <c r="D12" s="9" t="n"/>
@@ -1259,10 +1263,10 @@
         <v/>
       </c>
       <c r="F12" s="10" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="H12" s="10" t="inlineStr">
         <is>
@@ -1271,30 +1275,34 @@
       </c>
       <c r="I12" s="11" t="inlineStr">
         <is>
-          <t>Cannot wrap. Past ~9 characters it collides with the stat beside it.</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[0].value</t>
+          <t>POOLS[0].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Stat 1 label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>AI-first services opportunity by 2030</t>
+          <t>Policy and claims data sat in twelve systems with no shared definitions.</t>
         </is>
       </c>
       <c r="D13" s="9" t="n"/>
@@ -1303,10 +1311,10 @@
         <v/>
       </c>
       <c r="F13" s="10" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="G13" s="10" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
@@ -1315,30 +1323,34 @@
       </c>
       <c r="I13" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: locked to two lines. A third breaks the row baseline.</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[0].label</t>
+          <t>POOLS[0].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="14" ht="46" customHeight="1">
       <c r="A14" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Stat 2 figure</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>Built an AI-ready data platform with lineage, fingerprinting and synthetic augmentation for sparse claim types.</t>
         </is>
       </c>
       <c r="D14" s="9" t="n"/>
@@ -1347,10 +1359,10 @@
         <v/>
       </c>
       <c r="F14" s="10" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="G14" s="10" t="n">
-        <v>9</v>
+        <v>115</v>
       </c>
       <c r="H14" s="10" t="inlineStr">
         <is>
@@ -1359,30 +1371,34 @@
       </c>
       <c r="I14" s="11" t="inlineStr">
         <is>
-          <t>Cannot wrap. Past ~9 characters it collides with the stat beside it.</t>
-        </is>
-      </c>
-      <c r="J14" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J14" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[1].value</t>
+          <t>POOLS[0].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="15" ht="46" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Stat 2 label</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
         <is>
-          <t>of our top 200 clients on an AI journey</t>
+          <t>One trusted claims record feeding underwriting and fraud models.</t>
         </is>
       </c>
       <c r="D15" s="9" t="n"/>
@@ -1391,10 +1407,10 @@
         <v/>
       </c>
       <c r="F15" s="10" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="G15" s="10" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="H15" s="10" t="inlineStr">
         <is>
@@ -1403,30 +1419,34 @@
       </c>
       <c r="I15" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: locked to two lines. A third breaks the row baseline.</t>
-        </is>
-      </c>
-      <c r="J15" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J15" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K15" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[1].label</t>
+          <t>POOLS[0].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="16" ht="46" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Stat 3 figure</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>400+</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="D16" s="9" t="n"/>
@@ -1435,46 +1455,46 @@
         <v/>
       </c>
       <c r="F16" s="10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G16" s="10" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H16" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I16" s="11" t="inlineStr">
         <is>
-          <t>Cannot wrap. Past ~9 characters it collides with the stat beside it.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J16" s="11" t="inlineStr">
         <is>
-          <t>NEEDS NITIN SIGN-OFF. 400+ was inferred from the 14 Aug review (403 tagged, client-masked). Confirm it is public-safe and current, or replace.</t>
+          <t>Placeholder. No real client detail.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[2].value</t>
+          <t>POOLS[0].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="17" ht="46" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
-          <t>02 Stats</t>
+          <t>Pool 1 case 1</t>
         </is>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Stat 3 label</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>client case studies behind the framework</t>
+          <t>faster model onboarding</t>
         </is>
       </c>
       <c r="D17" s="9" t="n"/>
@@ -1483,46 +1503,46 @@
         <v/>
       </c>
       <c r="F17" s="10" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G17" s="10" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="H17" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I17" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: locked to two lines. A third breaks the row baseline.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J17" s="11" t="inlineStr">
         <is>
-          <t>Tied to the figure above.</t>
+          <t>Placeholder. No real client detail.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>BRAND.facts[2].label</t>
+          <t>POOLS[0].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="A18" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 — Data for AI</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>INSIGHT</t>
+          <t>North American retailer</t>
         </is>
       </c>
       <c r="D18" s="9" t="n"/>
@@ -1531,10 +1551,10 @@
         <v/>
       </c>
       <c r="F18" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G18" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H18" s="10" t="inlineStr">
         <is>
@@ -1543,20 +1563,24 @@
       </c>
       <c r="I18" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J18" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J18" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K18" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].verb</t>
+          <t>POOLS[0].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="19" ht="46" customHeight="1">
       <c r="A19" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 — Data for AI</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
@@ -1566,7 +1590,7 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Data for AI</t>
+          <t>Unstructured product data made usable</t>
         </is>
       </c>
       <c r="D19" s="9" t="n"/>
@@ -1575,10 +1599,10 @@
         <v/>
       </c>
       <c r="F19" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G19" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H19" s="10" t="inlineStr">
         <is>
@@ -1587,30 +1611,34 @@
       </c>
       <c r="I19" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J19" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J19" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K19" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].title</t>
+          <t>POOLS[0].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="20" ht="46" customHeight="1">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 — Data for AI</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Raw enterprise data becomes a trusted, model-ready asset, so analytics and prediction run on one version of the truth. We build the platforms that get it there, and use fingerprinting and synthetic data to fill the gaps privacy leaves behind. What comes out the other side is decisions made in real time, not reports written after the fact.</t>
+          <t>Two million product descriptions and images carried no consistent structure.</t>
         </is>
       </c>
       <c r="D20" s="9" t="n"/>
@@ -1619,10 +1647,10 @@
         <v/>
       </c>
       <c r="F20" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G20" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
@@ -1631,30 +1659,34 @@
       </c>
       <c r="I20" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J20" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J20" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K20" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].description</t>
+          <t>POOLS[0].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="21" ht="46" customHeight="1">
       <c r="A21" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>Global insurer</t>
+          <t>Applied AI-grade data engineering to extract, normalise and enrich attributes at scale.</t>
         </is>
       </c>
       <c r="D21" s="9" t="n"/>
@@ -1663,19 +1695,19 @@
         <v/>
       </c>
       <c r="F21" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G21" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I21" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J21" s="11" t="inlineStr">
@@ -1685,24 +1717,24 @@
       </c>
       <c r="K21" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].client</t>
+          <t>POOLS[0].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="22" ht="46" customHeight="1">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Claims data unified for model readiness</t>
+          <t>Search and recommendation models trained on a single catalogue.</t>
         </is>
       </c>
       <c r="D22" s="9" t="n"/>
@@ -1711,10 +1743,10 @@
         <v/>
       </c>
       <c r="F22" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G22" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
@@ -1723,7 +1755,7 @@
       </c>
       <c r="I22" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J22" s="11" t="inlineStr">
@@ -1733,24 +1765,24 @@
       </c>
       <c r="K22" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].title</t>
+          <t>POOLS[0].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="23" ht="46" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Policy and claims data sat in twelve systems with no shared definitions.</t>
+          <t>3x</t>
         </is>
       </c>
       <c r="D23" s="9" t="n"/>
@@ -1759,19 +1791,19 @@
         <v/>
       </c>
       <c r="F23" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G23" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I23" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J23" s="11" t="inlineStr">
@@ -1781,24 +1813,24 @@
       </c>
       <c r="K23" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].challenge</t>
+          <t>POOLS[0].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="24" ht="46" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 2</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Built an AI-ready data platform with lineage, fingerprinting and synthetic augmentation for sparse claim types.</t>
+          <t>attribute coverage</t>
         </is>
       </c>
       <c r="D24" s="9" t="n"/>
@@ -1807,19 +1839,19 @@
         <v/>
       </c>
       <c r="F24" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G24" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H24" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I24" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J24" s="11" t="inlineStr">
@@ -1829,24 +1861,24 @@
       </c>
       <c r="K24" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].action</t>
+          <t>POOLS[0].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="25" ht="46" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>One trusted claims record feeding underwriting and fraud models.</t>
+          <t>European bank</t>
         </is>
       </c>
       <c r="D25" s="9" t="n"/>
@@ -1855,19 +1887,19 @@
         <v/>
       </c>
       <c r="F25" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G25" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H25" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J25" s="11" t="inlineStr">
@@ -1877,24 +1909,24 @@
       </c>
       <c r="K25" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].outcome</t>
+          <t>POOLS[0].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="26" ht="46" customHeight="1">
       <c r="A26" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>Synthetic data unlocked restricted training</t>
         </is>
       </c>
       <c r="D26" s="9" t="n"/>
@@ -1903,19 +1935,19 @@
         <v/>
       </c>
       <c r="F26" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G26" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H26" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I26" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J26" s="11" t="inlineStr">
@@ -1925,24 +1957,24 @@
       </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].metric.value</t>
+          <t>POOLS[0].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="27" ht="46" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 1</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>faster model onboarding</t>
+          <t>Privacy rules blocked the use of real customer records in model development.</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -1951,19 +1983,19 @@
         <v/>
       </c>
       <c r="F27" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G27" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H27" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I27" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J27" s="11" t="inlineStr">
@@ -1973,24 +2005,24 @@
       </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[0].metric.label</t>
+          <t>POOLS[0].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="28" ht="46" customHeight="1">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>North American retailer</t>
+          <t>Generated statistically faithful synthetic datasets with fingerprinting to prove provenance.</t>
         </is>
       </c>
       <c r="D28" s="9" t="n"/>
@@ -1999,19 +2031,19 @@
         <v/>
       </c>
       <c r="F28" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G28" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H28" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I28" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J28" s="11" t="inlineStr">
@@ -2021,24 +2053,24 @@
       </c>
       <c r="K28" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].client</t>
+          <t>POOLS[0].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="29" ht="46" customHeight="1">
       <c r="A29" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>Unstructured product data made usable</t>
+          <t>Model development continued without exposing customer data.</t>
         </is>
       </c>
       <c r="D29" s="9" t="n"/>
@@ -2047,10 +2079,10 @@
         <v/>
       </c>
       <c r="F29" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G29" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H29" s="10" t="inlineStr">
         <is>
@@ -2059,7 +2091,7 @@
       </c>
       <c r="I29" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J29" s="11" t="inlineStr">
@@ -2069,24 +2101,24 @@
       </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].title</t>
+          <t>POOLS[0].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="30" ht="46" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Two million product descriptions and images carried no consistent structure.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D30" s="9" t="n"/>
@@ -2095,19 +2127,19 @@
         <v/>
       </c>
       <c r="F30" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G30" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H30" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I30" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J30" s="11" t="inlineStr">
@@ -2117,24 +2149,24 @@
       </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].challenge</t>
+          <t>POOLS[0].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="31" ht="46" customHeight="1">
       <c r="A31" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 1 case 3</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>Applied AI-grade data engineering to extract, normalise and enrich attributes at scale.</t>
+          <t>records exposed</t>
         </is>
       </c>
       <c r="D31" s="9" t="n"/>
@@ -2143,19 +2175,19 @@
         <v/>
       </c>
       <c r="F31" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G31" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H31" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I31" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J31" s="11" t="inlineStr">
@@ -2165,24 +2197,24 @@
       </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].action</t>
+          <t>POOLS[0].cases[2].metric.label</t>
         </is>
       </c>
     </row>
     <row r="32" ht="46" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 2 — AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Search and recommendation models trained on a single catalogue.</t>
+          <t>ORCHESTRATE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n"/>
@@ -2191,46 +2223,42 @@
         <v/>
       </c>
       <c r="F32" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G32" s="10" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="H32" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I32" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
+        </is>
+      </c>
+      <c r="J32" s="11" t="inlineStr"/>
       <c r="K32" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].outcome</t>
+          <t>POOLS[1].verb</t>
         </is>
       </c>
     </row>
     <row r="33" ht="46" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 2 — AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>3x</t>
+          <t>AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="D33" s="9" t="n"/>
@@ -2239,46 +2267,42 @@
         <v/>
       </c>
       <c r="F33" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G33" s="10" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H33" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I33" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J33" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
+        </is>
+      </c>
+      <c r="J33" s="11" t="inlineStr"/>
       <c r="K33" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].metric.value</t>
+          <t>POOLS[1].title</t>
         </is>
       </c>
     </row>
     <row r="34" ht="46" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 2</t>
+          <t>Pool 2 — AI Strategy &amp; Engineering</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>attribute coverage</t>
+          <t>One enterprise-wide AI operating model, rather than a hundred pilots that never leave their business unit. Agents, platforms and third-party tools run as one estate on infrastructure built for the workload. The architecture follows how the business works, not the tools that arrived first.</t>
         </is>
       </c>
       <c r="D34" s="9" t="n"/>
@@ -2287,36 +2311,32 @@
         <v/>
       </c>
       <c r="F34" s="10" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G34" s="10" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="H34" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I34" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J34" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
+        </is>
+      </c>
+      <c r="J34" s="11" t="inlineStr"/>
       <c r="K34" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[1].metric.label</t>
+          <t>POOLS[1].description</t>
         </is>
       </c>
     </row>
     <row r="35" ht="46" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2326,7 +2346,7 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>European bank</t>
+          <t>Global manufacturer</t>
         </is>
       </c>
       <c r="D35" s="9" t="n"/>
@@ -2357,14 +2377,14 @@
       </c>
       <c r="K35" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].client</t>
+          <t>POOLS[1].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="36" ht="46" customHeight="1">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
@@ -2374,7 +2394,7 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Synthetic data unlocked restricted training</t>
+          <t>From ninety pilots to one operating model</t>
         </is>
       </c>
       <c r="D36" s="9" t="n"/>
@@ -2405,14 +2425,14 @@
       </c>
       <c r="K36" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].title</t>
+          <t>POOLS[1].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="37" ht="46" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -2422,7 +2442,7 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Privacy rules blocked the use of real customer records in model development.</t>
+          <t>Business units were each running their own disconnected AI experiments.</t>
         </is>
       </c>
       <c r="D37" s="9" t="n"/>
@@ -2453,14 +2473,14 @@
       </c>
       <c r="K37" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].challenge</t>
+          <t>POOLS[1].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="38" ht="46" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -2470,7 +2490,7 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Generated statistically faithful synthetic datasets with fingerprinting to prove provenance.</t>
+          <t>Defined a single enterprise AI operating model and stood up shared platform and agent orchestration.</t>
         </is>
       </c>
       <c r="D38" s="9" t="n"/>
@@ -2501,14 +2521,14 @@
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].action</t>
+          <t>POOLS[1].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="39" ht="46" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -2518,7 +2538,7 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Model development continued without exposing customer data.</t>
+          <t>One governed route from idea to production for every unit.</t>
         </is>
       </c>
       <c r="D39" s="9" t="n"/>
@@ -2549,14 +2569,14 @@
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].outcome</t>
+          <t>POOLS[1].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="40" ht="46" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -2566,7 +2586,7 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D40" s="9" t="n"/>
@@ -2597,14 +2617,14 @@
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].metric.value</t>
+          <t>POOLS[1].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="41" ht="46" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>Pool 1 case 3</t>
+          <t>Pool 2 case 1</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -2614,7 +2634,7 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>records exposed</t>
+          <t>pilots consolidated</t>
         </is>
       </c>
       <c r="D41" s="9" t="n"/>
@@ -2645,24 +2665,24 @@
       </c>
       <c r="K41" s="12" t="inlineStr">
         <is>
-          <t>POOLS[0].cases[2].metric.label</t>
+          <t>POOLS[1].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="42" ht="46" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 — AI Strategy &amp; Engineering</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>ORCHESTRATE</t>
+          <t>Telecommunications group</t>
         </is>
       </c>
       <c r="D42" s="9" t="n"/>
@@ -2671,10 +2691,10 @@
         <v/>
       </c>
       <c r="F42" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G42" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H42" s="10" t="inlineStr">
         <is>
@@ -2683,20 +2703,24 @@
       </c>
       <c r="I42" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J42" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J42" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].verb</t>
+          <t>POOLS[1].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="43" ht="46" customHeight="1">
       <c r="A43" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 — AI Strategy &amp; Engineering</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -2706,7 +2730,7 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>AI Strategy &amp; Engineering</t>
+          <t>Purpose-built infrastructure for scale</t>
         </is>
       </c>
       <c r="D43" s="9" t="n"/>
@@ -2715,10 +2739,10 @@
         <v/>
       </c>
       <c r="F43" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G43" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
@@ -2727,30 +2751,34 @@
       </c>
       <c r="I43" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J43" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J43" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].title</t>
+          <t>POOLS[1].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="44" ht="46" customHeight="1">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 — AI Strategy &amp; Engineering</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>One enterprise-wide AI operating model, rather than a hundred pilots that never leave their business unit. Agents, platforms and third-party tools run as one estate on infrastructure built for the workload. The architecture follows how the business works, not the tools that arrived first.</t>
+          <t>General-purpose cloud could not carry inference cost or latency targets.</t>
         </is>
       </c>
       <c r="D44" s="9" t="n"/>
@@ -2759,10 +2787,10 @@
         <v/>
       </c>
       <c r="F44" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G44" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H44" s="10" t="inlineStr">
         <is>
@@ -2771,30 +2799,34 @@
       </c>
       <c r="I44" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J44" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J44" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K44" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].description</t>
+          <t>POOLS[1].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="45" ht="46" customHeight="1">
       <c r="A45" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>Global manufacturer</t>
+          <t>Designed and built dedicated AI infrastructure with workload-aware routing across models.</t>
         </is>
       </c>
       <c r="D45" s="9" t="n"/>
@@ -2803,19 +2835,19 @@
         <v/>
       </c>
       <c r="F45" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G45" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I45" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J45" s="11" t="inlineStr">
@@ -2825,24 +2857,24 @@
       </c>
       <c r="K45" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].client</t>
+          <t>POOLS[1].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="46" ht="46" customHeight="1">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>From ninety pilots to one operating model</t>
+          <t>Inference costs brought under control at production volume.</t>
         </is>
       </c>
       <c r="D46" s="9" t="n"/>
@@ -2851,10 +2883,10 @@
         <v/>
       </c>
       <c r="F46" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G46" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H46" s="10" t="inlineStr">
         <is>
@@ -2863,7 +2895,7 @@
       </c>
       <c r="I46" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J46" s="11" t="inlineStr">
@@ -2873,24 +2905,24 @@
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].title</t>
+          <t>POOLS[1].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="47" ht="46" customHeight="1">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Business units were each running their own disconnected AI experiments.</t>
+          <t>55%</t>
         </is>
       </c>
       <c r="D47" s="9" t="n"/>
@@ -2899,19 +2931,19 @@
         <v/>
       </c>
       <c r="F47" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G47" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H47" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I47" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J47" s="11" t="inlineStr">
@@ -2921,24 +2953,24 @@
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].challenge</t>
+          <t>POOLS[1].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="48" ht="46" customHeight="1">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 2</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Defined a single enterprise AI operating model and stood up shared platform and agent orchestration.</t>
+          <t>lower cost per call</t>
         </is>
       </c>
       <c r="D48" s="9" t="n"/>
@@ -2947,19 +2979,19 @@
         <v/>
       </c>
       <c r="F48" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G48" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H48" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I48" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J48" s="11" t="inlineStr">
@@ -2969,24 +3001,24 @@
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].action</t>
+          <t>POOLS[1].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="49" ht="46" customHeight="1">
       <c r="A49" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>One governed route from idea to production for every unit.</t>
+          <t>Energy utility</t>
         </is>
       </c>
       <c r="D49" s="9" t="n"/>
@@ -2995,19 +3027,19 @@
         <v/>
       </c>
       <c r="F49" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G49" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H49" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I49" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J49" s="11" t="inlineStr">
@@ -3017,24 +3049,24 @@
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].outcome</t>
+          <t>POOLS[1].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="50" ht="46" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>Agents, platforms and third-party tools in concert</t>
         </is>
       </c>
       <c r="D50" s="9" t="n"/>
@@ -3043,19 +3075,19 @@
         <v/>
       </c>
       <c r="F50" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G50" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H50" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I50" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J50" s="11" t="inlineStr">
@@ -3065,24 +3097,24 @@
       </c>
       <c r="K50" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].metric.value</t>
+          <t>POOLS[1].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="51" ht="46" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 1</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
         <is>
-          <t>pilots consolidated</t>
+          <t>Vendor tools and in-house agents could not interoperate or share context.</t>
         </is>
       </c>
       <c r="D51" s="9" t="n"/>
@@ -3091,19 +3123,19 @@
         <v/>
       </c>
       <c r="F51" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G51" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H51" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I51" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J51" s="11" t="inlineStr">
@@ -3113,24 +3145,24 @@
       </c>
       <c r="K51" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[0].metric.label</t>
+          <t>POOLS[1].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="52" ht="46" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>Telecommunications group</t>
+          <t>Built an orchestration layer so agents, proprietary platforms and third-party tools work as one estate.</t>
         </is>
       </c>
       <c r="D52" s="9" t="n"/>
@@ -3139,19 +3171,19 @@
         <v/>
       </c>
       <c r="F52" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G52" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H52" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I52" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J52" s="11" t="inlineStr">
@@ -3161,24 +3193,24 @@
       </c>
       <c r="K52" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].client</t>
+          <t>POOLS[1].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="53" ht="46" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
         <is>
-          <t>Purpose-built infrastructure for scale</t>
+          <t>New capability plugs in without a rebuild.</t>
         </is>
       </c>
       <c r="D53" s="9" t="n"/>
@@ -3187,10 +3219,10 @@
         <v/>
       </c>
       <c r="F53" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G53" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H53" s="10" t="inlineStr">
         <is>
@@ -3199,7 +3231,7 @@
       </c>
       <c r="I53" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J53" s="11" t="inlineStr">
@@ -3209,24 +3241,24 @@
       </c>
       <c r="K53" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].title</t>
+          <t>POOLS[1].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="54" ht="46" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>General-purpose cloud could not carry inference cost or latency targets.</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D54" s="9" t="n"/>
@@ -3235,19 +3267,19 @@
         <v/>
       </c>
       <c r="F54" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G54" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H54" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I54" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J54" s="11" t="inlineStr">
@@ -3257,24 +3289,24 @@
       </c>
       <c r="K54" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].challenge</t>
+          <t>POOLS[1].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="55" ht="46" customHeight="1">
       <c r="A55" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 2 case 3</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>Designed and built dedicated AI infrastructure with workload-aware routing across models.</t>
+          <t>weeks to onboard a tool</t>
         </is>
       </c>
       <c r="D55" s="9" t="n"/>
@@ -3283,19 +3315,19 @@
         <v/>
       </c>
       <c r="F55" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G55" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H55" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I55" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J55" s="11" t="inlineStr">
@@ -3305,24 +3337,24 @@
       </c>
       <c r="K55" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].action</t>
+          <t>POOLS[1].cases[2].metric.label</t>
         </is>
       </c>
     </row>
     <row r="56" ht="46" customHeight="1">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 3 — AI Trust</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>Inference costs brought under control at production volume.</t>
+          <t>ASSURE</t>
         </is>
       </c>
       <c r="D56" s="9" t="n"/>
@@ -3331,46 +3363,42 @@
         <v/>
       </c>
       <c r="F56" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G56" s="10" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="H56" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I56" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J56" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="inlineStr"/>
       <c r="K56" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].outcome</t>
+          <t>POOLS[2].verb</t>
         </is>
       </c>
     </row>
     <row r="57" ht="46" customHeight="1">
       <c r="A57" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 3 — AI Trust</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>AI Trust</t>
         </is>
       </c>
       <c r="D57" s="9" t="n"/>
@@ -3379,46 +3407,42 @@
         <v/>
       </c>
       <c r="F57" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G57" s="10" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H57" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I57" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J57" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="inlineStr"/>
       <c r="K57" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].metric.value</t>
+          <t>POOLS[2].title</t>
         </is>
       </c>
     </row>
     <row r="58" ht="46" customHeight="1">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 2</t>
+          <t>Pool 3 — AI Trust</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>lower cost per call</t>
+          <t>Responsible, secure and governed AI across the whole lifecycle, so it can scale without outrunning its guardrails. Risk assessment and policy design come first, and agents are security tested like any other system that reaches production. Governance is built to satisfy the regulator rather than the slide.</t>
         </is>
       </c>
       <c r="D58" s="9" t="n"/>
@@ -3427,36 +3451,32 @@
         <v/>
       </c>
       <c r="F58" s="10" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G58" s="10" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="H58" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I58" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J58" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="inlineStr"/>
       <c r="K58" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[1].metric.label</t>
+          <t>POOLS[2].description</t>
         </is>
       </c>
     </row>
     <row r="59" ht="46" customHeight="1">
       <c r="A59" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -3466,7 +3486,7 @@
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>Energy utility</t>
+          <t>Global bank</t>
         </is>
       </c>
       <c r="D59" s="9" t="n"/>
@@ -3497,14 +3517,14 @@
       </c>
       <c r="K59" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].client</t>
+          <t>POOLS[2].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="60" ht="46" customHeight="1">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -3514,7 +3534,7 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>Agents, platforms and third-party tools in concert</t>
+          <t>Agents governed across the lifecycle</t>
         </is>
       </c>
       <c r="D60" s="9" t="n"/>
@@ -3545,14 +3565,14 @@
       </c>
       <c r="K60" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].title</t>
+          <t>POOLS[2].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="61" ht="46" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -3562,7 +3582,7 @@
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>Vendor tools and in-house agents could not interoperate or share context.</t>
+          <t>Agents were reaching production faster than risk assessment could review them.</t>
         </is>
       </c>
       <c r="D61" s="9" t="n"/>
@@ -3593,14 +3613,14 @@
       </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].challenge</t>
+          <t>POOLS[2].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="62" ht="46" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -3610,7 +3630,7 @@
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>Built an orchestration layer so agents, proprietary platforms and third-party tools work as one estate.</t>
+          <t>Embedded risk assessment and policy design into the delivery path rather than after it.</t>
         </is>
       </c>
       <c r="D62" s="9" t="n"/>
@@ -3641,14 +3661,14 @@
       </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].action</t>
+          <t>POOLS[2].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="63" ht="46" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
@@ -3658,7 +3678,7 @@
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>New capability plugs in without a rebuild.</t>
+          <t>Every agent carries an assessment before it ships.</t>
         </is>
       </c>
       <c r="D63" s="9" t="n"/>
@@ -3689,14 +3709,14 @@
       </c>
       <c r="K63" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].outcome</t>
+          <t>POOLS[2].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="64" ht="46" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
@@ -3706,7 +3726,7 @@
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="D64" s="9" t="n"/>
@@ -3737,14 +3757,14 @@
       </c>
       <c r="K64" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].metric.value</t>
+          <t>POOLS[2].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="65" ht="46" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
-          <t>Pool 2 case 3</t>
+          <t>Pool 3 case 1</t>
         </is>
       </c>
       <c r="B65" s="7" t="inlineStr">
@@ -3754,7 +3774,7 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>weeks to onboard a tool</t>
+          <t>agents assessed</t>
         </is>
       </c>
       <c r="D65" s="9" t="n"/>
@@ -3785,24 +3805,24 @@
       </c>
       <c r="K65" s="12" t="inlineStr">
         <is>
-          <t>POOLS[1].cases[2].metric.label</t>
+          <t>POOLS[2].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="66" ht="46" customHeight="1">
       <c r="A66" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 — AI Trust</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>ASSURE</t>
+          <t>Pharmaceutical company</t>
         </is>
       </c>
       <c r="D66" s="9" t="n"/>
@@ -3811,10 +3831,10 @@
         <v/>
       </c>
       <c r="F66" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G66" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H66" s="10" t="inlineStr">
         <is>
@@ -3823,20 +3843,24 @@
       </c>
       <c r="I66" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J66" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J66" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K66" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].verb</t>
+          <t>POOLS[2].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="67" ht="46" customHeight="1">
       <c r="A67" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 — AI Trust</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B67" s="7" t="inlineStr">
@@ -3846,7 +3870,7 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>AI Trust</t>
+          <t>Security testing built for agents</t>
         </is>
       </c>
       <c r="D67" s="9" t="n"/>
@@ -3855,10 +3879,10 @@
         <v/>
       </c>
       <c r="F67" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G67" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H67" s="10" t="inlineStr">
         <is>
@@ -3867,30 +3891,34 @@
       </c>
       <c r="I67" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J67" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J67" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].title</t>
+          <t>POOLS[2].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="68" ht="46" customHeight="1">
       <c r="A68" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 — AI Trust</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>Responsible, secure and governed AI across the whole lifecycle, so it can scale without outrunning its guardrails. Risk assessment and policy design come first, and agents are security tested like any other system that reaches production. Governance is built to satisfy the regulator rather than the slide.</t>
+          <t>Conventional application testing did not cover prompt injection or tool misuse.</t>
         </is>
       </c>
       <c r="D68" s="9" t="n"/>
@@ -3899,10 +3927,10 @@
         <v/>
       </c>
       <c r="F68" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G68" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H68" s="10" t="inlineStr">
         <is>
@@ -3911,30 +3939,34 @@
       </c>
       <c r="I68" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J68" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J68" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].description</t>
+          <t>POOLS[2].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="69" ht="46" customHeight="1">
       <c r="A69" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>Global bank</t>
+          <t>Established agent-specific red teaming and continuous security testing.</t>
         </is>
       </c>
       <c r="D69" s="9" t="n"/>
@@ -3943,19 +3975,19 @@
         <v/>
       </c>
       <c r="F69" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G69" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H69" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I69" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J69" s="11" t="inlineStr">
@@ -3965,24 +3997,24 @@
       </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].client</t>
+          <t>POOLS[2].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="70" ht="46" customHeight="1">
       <c r="A70" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>Agents governed across the lifecycle</t>
+          <t>Agent-specific failure modes found before release.</t>
         </is>
       </c>
       <c r="D70" s="9" t="n"/>
@@ -3991,10 +4023,10 @@
         <v/>
       </c>
       <c r="F70" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G70" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H70" s="10" t="inlineStr">
         <is>
@@ -4003,7 +4035,7 @@
       </c>
       <c r="I70" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J70" s="11" t="inlineStr">
@@ -4013,24 +4045,24 @@
       </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].title</t>
+          <t>POOLS[2].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="71" ht="46" customHeight="1">
       <c r="A71" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>Agents were reaching production faster than risk assessment could review them.</t>
+          <t>200+</t>
         </is>
       </c>
       <c r="D71" s="9" t="n"/>
@@ -4039,19 +4071,19 @@
         <v/>
       </c>
       <c r="F71" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G71" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H71" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I71" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J71" s="11" t="inlineStr">
@@ -4061,24 +4093,24 @@
       </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].challenge</t>
+          <t>POOLS[2].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="72" ht="46" customHeight="1">
       <c r="A72" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 2</t>
         </is>
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>Embedded risk assessment and policy design into the delivery path rather than after it.</t>
+          <t>attack paths tested</t>
         </is>
       </c>
       <c r="D72" s="9" t="n"/>
@@ -4087,19 +4119,19 @@
         <v/>
       </c>
       <c r="F72" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G72" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H72" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I72" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J72" s="11" t="inlineStr">
@@ -4109,24 +4141,24 @@
       </c>
       <c r="K72" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].action</t>
+          <t>POOLS[2].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="73" ht="46" customHeight="1">
       <c r="A73" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>Every agent carries an assessment before it ships.</t>
+          <t>Telecommunications provider</t>
         </is>
       </c>
       <c r="D73" s="9" t="n"/>
@@ -4135,19 +4167,19 @@
         <v/>
       </c>
       <c r="F73" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G73" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H73" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I73" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J73" s="11" t="inlineStr">
@@ -4157,24 +4189,24 @@
       </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].outcome</t>
+          <t>POOLS[2].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="74" ht="46" customHeight="1">
       <c r="A74" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>Regulatory readiness, evidenced</t>
         </is>
       </c>
       <c r="D74" s="9" t="n"/>
@@ -4183,19 +4215,19 @@
         <v/>
       </c>
       <c r="F74" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G74" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H74" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I74" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J74" s="11" t="inlineStr">
@@ -4205,24 +4237,24 @@
       </c>
       <c r="K74" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].metric.value</t>
+          <t>POOLS[2].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="75" ht="46" customHeight="1">
       <c r="A75" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 1</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
         <is>
-          <t>agents assessed</t>
+          <t>New AI regulation demanded evidence the organisation could not produce.</t>
         </is>
       </c>
       <c r="D75" s="9" t="n"/>
@@ -4231,19 +4263,19 @@
         <v/>
       </c>
       <c r="F75" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G75" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I75" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J75" s="11" t="inlineStr">
@@ -4253,24 +4285,24 @@
       </c>
       <c r="K75" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[0].metric.label</t>
+          <t>POOLS[2].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="76" ht="46" customHeight="1">
       <c r="A76" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>Pharmaceutical company</t>
+          <t>Built governance with traceable evidence from policy through to model behaviour.</t>
         </is>
       </c>
       <c r="D76" s="9" t="n"/>
@@ -4279,19 +4311,19 @@
         <v/>
       </c>
       <c r="F76" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G76" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H76" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I76" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J76" s="11" t="inlineStr">
@@ -4301,24 +4333,24 @@
       </c>
       <c r="K76" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].client</t>
+          <t>POOLS[2].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="77" ht="46" customHeight="1">
       <c r="A77" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>Security testing built for agents</t>
+          <t>Audit answered from the system of record.</t>
         </is>
       </c>
       <c r="D77" s="9" t="n"/>
@@ -4327,10 +4359,10 @@
         <v/>
       </c>
       <c r="F77" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G77" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H77" s="10" t="inlineStr">
         <is>
@@ -4339,7 +4371,7 @@
       </c>
       <c r="I77" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J77" s="11" t="inlineStr">
@@ -4349,24 +4381,24 @@
       </c>
       <c r="K77" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].title</t>
+          <t>POOLS[2].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="78" ht="46" customHeight="1">
       <c r="A78" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>Conventional application testing did not cover prompt injection or tool misuse.</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D78" s="9" t="n"/>
@@ -4375,19 +4407,19 @@
         <v/>
       </c>
       <c r="F78" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G78" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H78" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I78" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J78" s="11" t="inlineStr">
@@ -4397,24 +4429,24 @@
       </c>
       <c r="K78" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].challenge</t>
+          <t>POOLS[2].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="79" ht="46" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 3 case 3</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>Established agent-specific red teaming and continuous security testing.</t>
+          <t>regimes satisfied</t>
         </is>
       </c>
       <c r="D79" s="9" t="n"/>
@@ -4423,19 +4455,19 @@
         <v/>
       </c>
       <c r="F79" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G79" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H79" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I79" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J79" s="11" t="inlineStr">
@@ -4445,24 +4477,24 @@
       </c>
       <c r="K79" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].action</t>
+          <t>POOLS[2].cases[2].metric.label</t>
         </is>
       </c>
     </row>
     <row r="80" ht="46" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 4 — Physical AI</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>Agent-specific failure modes found before release.</t>
+          <t>INNOVATE</t>
         </is>
       </c>
       <c r="D80" s="9" t="n"/>
@@ -4471,46 +4503,42 @@
         <v/>
       </c>
       <c r="F80" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G80" s="10" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I80" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J80" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="inlineStr"/>
       <c r="K80" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].outcome</t>
+          <t>POOLS[3].verb</t>
         </is>
       </c>
     </row>
     <row r="81" ht="46" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 4 — Physical AI</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>200+</t>
+          <t>Physical AI</t>
         </is>
       </c>
       <c r="D81" s="9" t="n"/>
@@ -4519,46 +4547,42 @@
         <v/>
       </c>
       <c r="F81" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G81" s="10" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H81" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I81" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J81" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="inlineStr"/>
       <c r="K81" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].metric.value</t>
+          <t>POOLS[3].title</t>
         </is>
       </c>
     </row>
     <row r="82" ht="46" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 2</t>
+          <t>Pool 4 — Physical AI</t>
         </is>
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>attack paths tested</t>
+          <t>Intelligence embedded in products and operations, reading sensor signal and acting on it in real time. Digital twins, robotics and autonomy turn that signal into physical action on the floor and in the field. Enough of the model runs at the edge that the product keeps working when the network does not.</t>
         </is>
       </c>
       <c r="D82" s="9" t="n"/>
@@ -4567,36 +4591,32 @@
         <v/>
       </c>
       <c r="F82" s="10" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G82" s="10" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="H82" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I82" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J82" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="inlineStr"/>
       <c r="K82" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[1].metric.label</t>
+          <t>POOLS[3].description</t>
         </is>
       </c>
     </row>
     <row r="83" ht="46" customHeight="1">
       <c r="A83" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B83" s="7" t="inlineStr">
@@ -4606,7 +4626,7 @@
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>Telecommunications provider</t>
+          <t>Automotive manufacturer</t>
         </is>
       </c>
       <c r="D83" s="9" t="n"/>
@@ -4637,14 +4657,14 @@
       </c>
       <c r="K83" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].client</t>
+          <t>POOLS[3].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="84" ht="46" customHeight="1">
       <c r="A84" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B84" s="7" t="inlineStr">
@@ -4654,7 +4674,7 @@
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>Regulatory readiness, evidenced</t>
+          <t>Line-side quality that acts in real time</t>
         </is>
       </c>
       <c r="D84" s="9" t="n"/>
@@ -4685,14 +4705,14 @@
       </c>
       <c r="K84" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].title</t>
+          <t>POOLS[3].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="85" ht="46" customHeight="1">
       <c r="A85" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B85" s="7" t="inlineStr">
@@ -4702,7 +4722,7 @@
       </c>
       <c r="C85" s="8" t="inlineStr">
         <is>
-          <t>New AI regulation demanded evidence the organisation could not produce.</t>
+          <t>Defects were detected downstream, after value had already been added.</t>
         </is>
       </c>
       <c r="D85" s="9" t="n"/>
@@ -4733,14 +4753,14 @@
       </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].challenge</t>
+          <t>POOLS[3].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="86" ht="46" customHeight="1">
       <c r="A86" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B86" s="7" t="inlineStr">
@@ -4750,7 +4770,7 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>Built governance with traceable evidence from policy through to model behaviour.</t>
+          <t>Embedded edge intelligence at the line to interpret sensor and vision data and act within the cycle.</t>
         </is>
       </c>
       <c r="D86" s="9" t="n"/>
@@ -4781,14 +4801,14 @@
       </c>
       <c r="K86" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].action</t>
+          <t>POOLS[3].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="87" ht="46" customHeight="1">
       <c r="A87" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B87" s="7" t="inlineStr">
@@ -4798,7 +4818,7 @@
       </c>
       <c r="C87" s="8" t="inlineStr">
         <is>
-          <t>Audit answered from the system of record.</t>
+          <t>Defects caught at the station that caused them.</t>
         </is>
       </c>
       <c r="D87" s="9" t="n"/>
@@ -4829,14 +4849,14 @@
       </c>
       <c r="K87" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].outcome</t>
+          <t>POOLS[3].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="88" ht="46" customHeight="1">
       <c r="A88" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B88" s="7" t="inlineStr">
@@ -4846,7 +4866,7 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="D88" s="9" t="n"/>
@@ -4877,14 +4897,14 @@
       </c>
       <c r="K88" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].metric.value</t>
+          <t>POOLS[3].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="89" ht="46" customHeight="1">
       <c r="A89" s="7" t="inlineStr">
         <is>
-          <t>Pool 3 case 3</t>
+          <t>Pool 4 case 1</t>
         </is>
       </c>
       <c r="B89" s="7" t="inlineStr">
@@ -4894,7 +4914,7 @@
       </c>
       <c r="C89" s="8" t="inlineStr">
         <is>
-          <t>regimes satisfied</t>
+          <t>less rework</t>
         </is>
       </c>
       <c r="D89" s="9" t="n"/>
@@ -4925,24 +4945,24 @@
       </c>
       <c r="K89" s="12" t="inlineStr">
         <is>
-          <t>POOLS[2].cases[2].metric.label</t>
+          <t>POOLS[3].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="90" ht="46" customHeight="1">
       <c r="A90" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 — Physical AI</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>INNOVATE</t>
+          <t>Industrial equipment maker</t>
         </is>
       </c>
       <c r="D90" s="9" t="n"/>
@@ -4951,10 +4971,10 @@
         <v/>
       </c>
       <c r="F90" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G90" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H90" s="10" t="inlineStr">
         <is>
@@ -4963,20 +4983,24 @@
       </c>
       <c r="I90" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J90" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J90" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K90" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].verb</t>
+          <t>POOLS[3].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="91" ht="46" customHeight="1">
       <c r="A91" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 — Physical AI</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B91" s="7" t="inlineStr">
@@ -4986,7 +5010,7 @@
       </c>
       <c r="C91" s="8" t="inlineStr">
         <is>
-          <t>Physical AI</t>
+          <t>Digital twin drives the physical asset</t>
         </is>
       </c>
       <c r="D91" s="9" t="n"/>
@@ -4995,10 +5019,10 @@
         <v/>
       </c>
       <c r="F91" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G91" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H91" s="10" t="inlineStr">
         <is>
@@ -5007,30 +5031,34 @@
       </c>
       <c r="I91" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J91" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K91" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].title</t>
+          <t>POOLS[3].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="92" ht="46" customHeight="1">
       <c r="A92" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 — Physical AI</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>Intelligence embedded in products and operations, reading sensor signal and acting on it in real time. Digital twins, robotics and autonomy turn that signal into physical action on the floor and in the field. Enough of the model runs at the edge that the product keeps working when the network does not.</t>
+          <t>Field failures were expensive and impossible to predict from telemetry alone.</t>
         </is>
       </c>
       <c r="D92" s="9" t="n"/>
@@ -5039,10 +5067,10 @@
         <v/>
       </c>
       <c r="F92" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G92" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
@@ -5051,30 +5079,34 @@
       </c>
       <c r="I92" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J92" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K92" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].description</t>
+          <t>POOLS[3].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="93" ht="46" customHeight="1">
       <c r="A93" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C93" s="8" t="inlineStr">
         <is>
-          <t>Automotive manufacturer</t>
+          <t>Paired a digital twin with on-device intelligence to interpret signals and schedule intervention.</t>
         </is>
       </c>
       <c r="D93" s="9" t="n"/>
@@ -5083,19 +5115,19 @@
         <v/>
       </c>
       <c r="F93" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G93" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H93" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I93" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J93" s="11" t="inlineStr">
@@ -5105,24 +5137,24 @@
       </c>
       <c r="K93" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].client</t>
+          <t>POOLS[3].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="94" ht="46" customHeight="1">
       <c r="A94" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>Line-side quality that acts in real time</t>
+          <t>Maintenance moved from calendar to condition.</t>
         </is>
       </c>
       <c r="D94" s="9" t="n"/>
@@ -5131,10 +5163,10 @@
         <v/>
       </c>
       <c r="F94" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G94" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H94" s="10" t="inlineStr">
         <is>
@@ -5143,7 +5175,7 @@
       </c>
       <c r="I94" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J94" s="11" t="inlineStr">
@@ -5153,24 +5185,24 @@
       </c>
       <c r="K94" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].title</t>
+          <t>POOLS[3].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="95" ht="46" customHeight="1">
       <c r="A95" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C95" s="8" t="inlineStr">
         <is>
-          <t>Defects were detected downstream, after value had already been added.</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="D95" s="9" t="n"/>
@@ -5179,19 +5211,19 @@
         <v/>
       </c>
       <c r="F95" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G95" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H95" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I95" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J95" s="11" t="inlineStr">
@@ -5201,24 +5233,24 @@
       </c>
       <c r="K95" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].challenge</t>
+          <t>POOLS[3].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="96" ht="46" customHeight="1">
       <c r="A96" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 2</t>
         </is>
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>Embedded edge intelligence at the line to interpret sensor and vision data and act within the cycle.</t>
+          <t>fewer unplanned stops</t>
         </is>
       </c>
       <c r="D96" s="9" t="n"/>
@@ -5227,19 +5259,19 @@
         <v/>
       </c>
       <c r="F96" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G96" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H96" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I96" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J96" s="11" t="inlineStr">
@@ -5249,24 +5281,24 @@
       </c>
       <c r="K96" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].action</t>
+          <t>POOLS[3].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="97" ht="46" customHeight="1">
       <c r="A97" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C97" s="8" t="inlineStr">
         <is>
-          <t>Defects caught at the station that caused them.</t>
+          <t>Ports operator</t>
         </is>
       </c>
       <c r="D97" s="9" t="n"/>
@@ -5275,19 +5307,19 @@
         <v/>
       </c>
       <c r="F97" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G97" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H97" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I97" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J97" s="11" t="inlineStr">
@@ -5297,24 +5329,24 @@
       </c>
       <c r="K97" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].outcome</t>
+          <t>POOLS[3].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="98" ht="46" customHeight="1">
       <c r="A98" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>Autonomous handling in a live yard</t>
         </is>
       </c>
       <c r="D98" s="9" t="n"/>
@@ -5323,19 +5355,19 @@
         <v/>
       </c>
       <c r="F98" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G98" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H98" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I98" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J98" s="11" t="inlineStr">
@@ -5345,24 +5377,24 @@
       </c>
       <c r="K98" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].metric.value</t>
+          <t>POOLS[3].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="99" ht="46" customHeight="1">
       <c r="A99" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 1</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C99" s="8" t="inlineStr">
         <is>
-          <t>less rework</t>
+          <t>Container moves depended on manual coordination in a congested yard.</t>
         </is>
       </c>
       <c r="D99" s="9" t="n"/>
@@ -5371,19 +5403,19 @@
         <v/>
       </c>
       <c r="F99" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G99" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H99" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I99" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J99" s="11" t="inlineStr">
@@ -5393,24 +5425,24 @@
       </c>
       <c r="K99" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[0].metric.label</t>
+          <t>POOLS[3].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="100" ht="46" customHeight="1">
       <c r="A100" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>Industrial equipment maker</t>
+          <t>Combined robotics, edge perception and a live twin of the yard to sequence moves autonomously.</t>
         </is>
       </c>
       <c r="D100" s="9" t="n"/>
@@ -5419,19 +5451,19 @@
         <v/>
       </c>
       <c r="F100" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G100" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H100" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I100" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J100" s="11" t="inlineStr">
@@ -5441,24 +5473,24 @@
       </c>
       <c r="K100" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].client</t>
+          <t>POOLS[3].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="101" ht="46" customHeight="1">
       <c r="A101" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C101" s="8" t="inlineStr">
         <is>
-          <t>Digital twin drives the physical asset</t>
+          <t>Higher throughput on the same footprint.</t>
         </is>
       </c>
       <c r="D101" s="9" t="n"/>
@@ -5467,10 +5499,10 @@
         <v/>
       </c>
       <c r="F101" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G101" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H101" s="10" t="inlineStr">
         <is>
@@ -5479,7 +5511,7 @@
       </c>
       <c r="I101" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J101" s="11" t="inlineStr">
@@ -5489,24 +5521,24 @@
       </c>
       <c r="K101" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].title</t>
+          <t>POOLS[3].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="102" ht="46" customHeight="1">
       <c r="A102" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>Field failures were expensive and impossible to predict from telemetry alone.</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="D102" s="9" t="n"/>
@@ -5515,19 +5547,19 @@
         <v/>
       </c>
       <c r="F102" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G102" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H102" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I102" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J102" s="11" t="inlineStr">
@@ -5537,24 +5569,24 @@
       </c>
       <c r="K102" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].challenge</t>
+          <t>POOLS[3].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="103" ht="46" customHeight="1">
       <c r="A103" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 4 case 3</t>
         </is>
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C103" s="8" t="inlineStr">
         <is>
-          <t>Paired a digital twin with on-device intelligence to interpret signals and schedule intervention.</t>
+          <t>more moves per hour</t>
         </is>
       </c>
       <c r="D103" s="9" t="n"/>
@@ -5563,19 +5595,19 @@
         <v/>
       </c>
       <c r="F103" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G103" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H103" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I103" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J103" s="11" t="inlineStr">
@@ -5585,24 +5617,24 @@
       </c>
       <c r="K103" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].action</t>
+          <t>POOLS[3].cases[2].metric.label</t>
         </is>
       </c>
     </row>
     <row r="104" ht="46" customHeight="1">
       <c r="A104" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 5 — Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>Maintenance moved from calendar to condition.</t>
+          <t>MODERNIZE</t>
         </is>
       </c>
       <c r="D104" s="9" t="n"/>
@@ -5611,46 +5643,42 @@
         <v/>
       </c>
       <c r="F104" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G104" s="10" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="H104" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I104" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J104" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
+        </is>
+      </c>
+      <c r="J104" s="11" t="inlineStr"/>
       <c r="K104" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].outcome</t>
+          <t>POOLS[4].verb</t>
         </is>
       </c>
     </row>
     <row r="105" ht="46" customHeight="1">
       <c r="A105" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 5 — Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C105" s="8" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="D105" s="9" t="n"/>
@@ -5659,46 +5687,42 @@
         <v/>
       </c>
       <c r="F105" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G105" s="10" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H105" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I105" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J105" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
+        </is>
+      </c>
+      <c r="J105" s="11" t="inlineStr"/>
       <c r="K105" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].metric.value</t>
+          <t>POOLS[4].title</t>
         </is>
       </c>
     </row>
     <row r="106" ht="46" customHeight="1">
       <c r="A106" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 2</t>
+          <t>Pool 5 — Agentic Legacy Modernization</t>
         </is>
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>fewer unplanned stops</t>
+          <t>Agents read the legacy estate and recover what it was built to do, including the rules nobody wrote down and the people who knew them have left. Modernisation then happens progressively instead of as a big-bang rewrite. Technical debt comes down while the systems that run the business stay up.</t>
         </is>
       </c>
       <c r="D106" s="9" t="n"/>
@@ -5707,36 +5731,32 @@
         <v/>
       </c>
       <c r="F106" s="10" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G106" s="10" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="H106" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I106" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J106" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
+        </is>
+      </c>
+      <c r="J106" s="11" t="inlineStr"/>
       <c r="K106" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[1].metric.label</t>
+          <t>POOLS[4].description</t>
         </is>
       </c>
     </row>
     <row r="107" ht="46" customHeight="1">
       <c r="A107" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B107" s="7" t="inlineStr">
@@ -5746,7 +5766,7 @@
       </c>
       <c r="C107" s="8" t="inlineStr">
         <is>
-          <t>Ports operator</t>
+          <t>Retail bank</t>
         </is>
       </c>
       <c r="D107" s="9" t="n"/>
@@ -5777,14 +5797,14 @@
       </c>
       <c r="K107" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].client</t>
+          <t>POOLS[4].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="108" ht="46" customHeight="1">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B108" s="7" t="inlineStr">
@@ -5794,7 +5814,7 @@
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>Autonomous handling in a live yard</t>
+          <t>Core platform intent recovered by agents</t>
         </is>
       </c>
       <c r="D108" s="9" t="n"/>
@@ -5825,14 +5845,14 @@
       </c>
       <c r="K108" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].title</t>
+          <t>POOLS[4].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="109" ht="46" customHeight="1">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B109" s="7" t="inlineStr">
@@ -5842,7 +5862,7 @@
       </c>
       <c r="C109" s="8" t="inlineStr">
         <is>
-          <t>Container moves depended on manual coordination in a congested yard.</t>
+          <t>Four decades of core banking code with no reliable documentation.</t>
         </is>
       </c>
       <c r="D109" s="9" t="n"/>
@@ -5873,14 +5893,14 @@
       </c>
       <c r="K109" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].challenge</t>
+          <t>POOLS[4].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="110" ht="46" customHeight="1">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B110" s="7" t="inlineStr">
@@ -5890,7 +5910,7 @@
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>Combined robotics, edge perception and a live twin of the yard to sequence moves autonomously.</t>
+          <t>Agents reverse-engineered the estate to recover business intent before any code was rewritten.</t>
         </is>
       </c>
       <c r="D110" s="9" t="n"/>
@@ -5921,14 +5941,14 @@
       </c>
       <c r="K110" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].action</t>
+          <t>POOLS[4].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="111" ht="46" customHeight="1">
       <c r="A111" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B111" s="7" t="inlineStr">
@@ -5938,7 +5958,7 @@
       </c>
       <c r="C111" s="8" t="inlineStr">
         <is>
-          <t>Higher throughput on the same footprint.</t>
+          <t>Modernisation planned against what the system actually does.</t>
         </is>
       </c>
       <c r="D111" s="9" t="n"/>
@@ -5969,14 +5989,14 @@
       </c>
       <c r="K111" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].outcome</t>
+          <t>POOLS[4].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="112" ht="46" customHeight="1">
       <c r="A112" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B112" s="7" t="inlineStr">
@@ -5986,7 +6006,7 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>12M</t>
         </is>
       </c>
       <c r="D112" s="9" t="n"/>
@@ -6017,14 +6037,14 @@
       </c>
       <c r="K112" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].metric.value</t>
+          <t>POOLS[4].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="113" ht="46" customHeight="1">
       <c r="A113" s="7" t="inlineStr">
         <is>
-          <t>Pool 4 case 3</t>
+          <t>Pool 5 case 1</t>
         </is>
       </c>
       <c r="B113" s="7" t="inlineStr">
@@ -6034,7 +6054,7 @@
       </c>
       <c r="C113" s="8" t="inlineStr">
         <is>
-          <t>more moves per hour</t>
+          <t>lines analysed</t>
         </is>
       </c>
       <c r="D113" s="9" t="n"/>
@@ -6065,24 +6085,24 @@
       </c>
       <c r="K113" s="12" t="inlineStr">
         <is>
-          <t>POOLS[3].cases[2].metric.label</t>
+          <t>POOLS[4].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="114" ht="46" customHeight="1">
       <c r="A114" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 — Agentic Legacy Modernization</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B114" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>MODERNIZE</t>
+          <t>Public sector agency</t>
         </is>
       </c>
       <c r="D114" s="9" t="n"/>
@@ -6091,10 +6111,10 @@
         <v/>
       </c>
       <c r="F114" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G114" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H114" s="10" t="inlineStr">
         <is>
@@ -6103,20 +6123,24 @@
       </c>
       <c r="I114" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J114" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J114" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K114" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].verb</t>
+          <t>POOLS[4].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="115" ht="46" customHeight="1">
       <c r="A115" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 — Agentic Legacy Modernization</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B115" s="7" t="inlineStr">
@@ -6126,7 +6150,7 @@
       </c>
       <c r="C115" s="8" t="inlineStr">
         <is>
-          <t>Agentic Legacy Modernization</t>
+          <t>Progressive migration, no disruption</t>
         </is>
       </c>
       <c r="D115" s="9" t="n"/>
@@ -6135,10 +6159,10 @@
         <v/>
       </c>
       <c r="F115" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G115" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H115" s="10" t="inlineStr">
         <is>
@@ -6147,30 +6171,34 @@
       </c>
       <c r="I115" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J115" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K115" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].title</t>
+          <t>POOLS[4].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="116" ht="46" customHeight="1">
       <c r="A116" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 — Agentic Legacy Modernization</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B116" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>Agents read the legacy estate and recover what it was built to do, including the rules nobody wrote down and the people who knew them have left. Modernisation then happens progressively instead of as a big-bang rewrite. Technical debt comes down while the systems that run the business stay up.</t>
+          <t>A big-bang rewrite had already failed once and could not be attempted again.</t>
         </is>
       </c>
       <c r="D116" s="9" t="n"/>
@@ -6179,10 +6207,10 @@
         <v/>
       </c>
       <c r="F116" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G116" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H116" s="10" t="inlineStr">
         <is>
@@ -6191,30 +6219,34 @@
       </c>
       <c r="I116" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J116" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K116" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].description</t>
+          <t>POOLS[4].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="117" ht="46" customHeight="1">
       <c r="A117" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B117" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C117" s="8" t="inlineStr">
         <is>
-          <t>Retail bank</t>
+          <t>Modernised progressively behind stable interfaces, with each increment proven in production.</t>
         </is>
       </c>
       <c r="D117" s="9" t="n"/>
@@ -6223,19 +6255,19 @@
         <v/>
       </c>
       <c r="F117" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G117" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H117" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I117" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J117" s="11" t="inlineStr">
@@ -6245,24 +6277,24 @@
       </c>
       <c r="K117" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].client</t>
+          <t>POOLS[4].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="118" ht="46" customHeight="1">
       <c r="A118" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B118" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>Core platform intent recovered by agents</t>
+          <t>No service interruption during the programme.</t>
         </is>
       </c>
       <c r="D118" s="9" t="n"/>
@@ -6271,10 +6303,10 @@
         <v/>
       </c>
       <c r="F118" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G118" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H118" s="10" t="inlineStr">
         <is>
@@ -6283,7 +6315,7 @@
       </c>
       <c r="I118" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J118" s="11" t="inlineStr">
@@ -6293,24 +6325,24 @@
       </c>
       <c r="K118" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].title</t>
+          <t>POOLS[4].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="119" ht="46" customHeight="1">
       <c r="A119" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B119" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C119" s="8" t="inlineStr">
         <is>
-          <t>Four decades of core banking code with no reliable documentation.</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D119" s="9" t="n"/>
@@ -6319,19 +6351,19 @@
         <v/>
       </c>
       <c r="F119" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G119" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H119" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I119" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J119" s="11" t="inlineStr">
@@ -6341,24 +6373,24 @@
       </c>
       <c r="K119" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].challenge</t>
+          <t>POOLS[4].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="120" ht="46" customHeight="1">
       <c r="A120" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 2</t>
         </is>
       </c>
       <c r="B120" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>Agents reverse-engineered the estate to recover business intent before any code was rewritten.</t>
+          <t>hours of downtime</t>
         </is>
       </c>
       <c r="D120" s="9" t="n"/>
@@ -6367,19 +6399,19 @@
         <v/>
       </c>
       <c r="F120" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G120" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H120" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I120" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J120" s="11" t="inlineStr">
@@ -6389,24 +6421,24 @@
       </c>
       <c r="K120" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].action</t>
+          <t>POOLS[4].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="121" ht="46" customHeight="1">
       <c r="A121" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B121" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C121" s="8" t="inlineStr">
         <is>
-          <t>Modernisation planned against what the system actually does.</t>
+          <t>Insurance group</t>
         </is>
       </c>
       <c r="D121" s="9" t="n"/>
@@ -6415,19 +6447,19 @@
         <v/>
       </c>
       <c r="F121" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G121" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H121" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I121" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J121" s="11" t="inlineStr">
@@ -6437,24 +6469,24 @@
       </c>
       <c r="K121" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].outcome</t>
+          <t>POOLS[4].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="122" ht="46" customHeight="1">
       <c r="A122" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B122" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>12M</t>
+          <t>Technical debt cut without a rewrite</t>
         </is>
       </c>
       <c r="D122" s="9" t="n"/>
@@ -6463,19 +6495,19 @@
         <v/>
       </c>
       <c r="F122" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G122" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H122" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I122" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J122" s="11" t="inlineStr">
@@ -6485,24 +6517,24 @@
       </c>
       <c r="K122" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].metric.value</t>
+          <t>POOLS[4].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="123" ht="46" customHeight="1">
       <c r="A123" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 1</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B123" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C123" s="8" t="inlineStr">
         <is>
-          <t>lines analysed</t>
+          <t>Change requests took months because nobody could safely alter the policy engine.</t>
         </is>
       </c>
       <c r="D123" s="9" t="n"/>
@@ -6511,19 +6543,19 @@
         <v/>
       </c>
       <c r="F123" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G123" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H123" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I123" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J123" s="11" t="inlineStr">
@@ -6533,24 +6565,24 @@
       </c>
       <c r="K123" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[0].metric.label</t>
+          <t>POOLS[4].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="124" ht="46" customHeight="1">
       <c r="A124" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B124" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>Public sector agency</t>
+          <t>Used agents to map dependencies and safely decompose the engine into governed services.</t>
         </is>
       </c>
       <c r="D124" s="9" t="n"/>
@@ -6559,19 +6591,19 @@
         <v/>
       </c>
       <c r="F124" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G124" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H124" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I124" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J124" s="11" t="inlineStr">
@@ -6581,24 +6613,24 @@
       </c>
       <c r="K124" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].client</t>
+          <t>POOLS[4].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="125" ht="46" customHeight="1">
       <c r="A125" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B125" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C125" s="8" t="inlineStr">
         <is>
-          <t>Progressive migration, no disruption</t>
+          <t>Change velocity restored without replacing the platform.</t>
         </is>
       </c>
       <c r="D125" s="9" t="n"/>
@@ -6607,10 +6639,10 @@
         <v/>
       </c>
       <c r="F125" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G125" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H125" s="10" t="inlineStr">
         <is>
@@ -6619,7 +6651,7 @@
       </c>
       <c r="I125" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J125" s="11" t="inlineStr">
@@ -6629,24 +6661,24 @@
       </c>
       <c r="K125" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].title</t>
+          <t>POOLS[4].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="126" ht="46" customHeight="1">
       <c r="A126" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B126" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>A big-bang rewrite had already failed once and could not be attempted again.</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="D126" s="9" t="n"/>
@@ -6655,19 +6687,19 @@
         <v/>
       </c>
       <c r="F126" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G126" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H126" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I126" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J126" s="11" t="inlineStr">
@@ -6677,24 +6709,24 @@
       </c>
       <c r="K126" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].challenge</t>
+          <t>POOLS[4].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="127" ht="46" customHeight="1">
       <c r="A127" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 5 case 3</t>
         </is>
       </c>
       <c r="B127" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C127" s="8" t="inlineStr">
         <is>
-          <t>Modernised progressively behind stable interfaces, with each increment proven in production.</t>
+          <t>faster change cycle</t>
         </is>
       </c>
       <c r="D127" s="9" t="n"/>
@@ -6703,19 +6735,19 @@
         <v/>
       </c>
       <c r="F127" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G127" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H127" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I127" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J127" s="11" t="inlineStr">
@@ -6725,24 +6757,24 @@
       </c>
       <c r="K127" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].action</t>
+          <t>POOLS[4].cases[2].metric.label</t>
         </is>
       </c>
     </row>
     <row r="128" ht="46" customHeight="1">
       <c r="A128" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 6 — Process AI</t>
         </is>
       </c>
       <c r="B128" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Eyebrow verb</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>No service interruption during the programme.</t>
+          <t>TRANSFORM</t>
         </is>
       </c>
       <c r="D128" s="9" t="n"/>
@@ -6751,46 +6783,42 @@
         <v/>
       </c>
       <c r="F128" s="10" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="G128" s="10" t="n">
-        <v>110</v>
+        <v>15</v>
       </c>
       <c r="H128" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I128" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J128" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>Small caption inside the hexagon piece, above the pool name.</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="inlineStr"/>
       <c r="K128" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].outcome</t>
+          <t>POOLS[5].verb</t>
         </is>
       </c>
     </row>
     <row r="129" ht="46" customHeight="1">
       <c r="A129" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 6 — Process AI</t>
         </is>
       </c>
       <c r="B129" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C129" s="8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Process AI</t>
         </is>
       </c>
       <c r="D129" s="9" t="n"/>
@@ -6799,46 +6827,42 @@
         <v/>
       </c>
       <c r="F129" s="10" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G129" s="10" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="H129" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I129" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J129" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
+        </is>
+      </c>
+      <c r="J129" s="11" t="inlineStr"/>
       <c r="K129" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].metric.value</t>
+          <t>POOLS[5].title</t>
         </is>
       </c>
     </row>
     <row r="130" ht="46" customHeight="1">
       <c r="A130" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 2</t>
+          <t>Pool 6 — Process AI</t>
         </is>
       </c>
       <c r="B130" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>hours of downtime</t>
+          <t>End-to-end workflows redesigned around domain-aware agents that understand the work, not just the words. They run alongside the people who own the outcome, who stay in the loop where judgement is needed. That combination is what turns incremental savings into a step change in both efficiency and experience.</t>
         </is>
       </c>
       <c r="D130" s="9" t="n"/>
@@ -6847,36 +6871,32 @@
         <v/>
       </c>
       <c r="F130" s="10" t="n">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G130" s="10" t="n">
-        <v>28</v>
+        <v>340</v>
       </c>
       <c r="H130" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I130" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J130" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
+          <t>MEASURED: the buttons below drop at 384 characters.</t>
+        </is>
+      </c>
+      <c r="J130" s="11" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[1].metric.label</t>
+          <t>POOLS[5].description</t>
         </is>
       </c>
     </row>
     <row r="131" ht="46" customHeight="1">
       <c r="A131" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B131" s="7" t="inlineStr">
@@ -6886,7 +6906,7 @@
       </c>
       <c r="C131" s="8" t="inlineStr">
         <is>
-          <t>Insurance group</t>
+          <t>Consumer goods company</t>
         </is>
       </c>
       <c r="D131" s="9" t="n"/>
@@ -6917,14 +6937,14 @@
       </c>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].client</t>
+          <t>POOLS[5].cases[0].client</t>
         </is>
       </c>
     </row>
     <row r="132" ht="46" customHeight="1">
       <c r="A132" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B132" s="7" t="inlineStr">
@@ -6934,7 +6954,7 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>Technical debt cut without a rewrite</t>
+          <t>Order to cash rebuilt around agents</t>
         </is>
       </c>
       <c r="D132" s="9" t="n"/>
@@ -6965,14 +6985,14 @@
       </c>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].title</t>
+          <t>POOLS[5].cases[0].title</t>
         </is>
       </c>
     </row>
     <row r="133" ht="46" customHeight="1">
       <c r="A133" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B133" s="7" t="inlineStr">
@@ -6982,7 +7002,7 @@
       </c>
       <c r="C133" s="8" t="inlineStr">
         <is>
-          <t>Change requests took months because nobody could safely alter the policy engine.</t>
+          <t>Order exceptions were handled manually across three shared service centres.</t>
         </is>
       </c>
       <c r="D133" s="9" t="n"/>
@@ -7013,14 +7033,14 @@
       </c>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].challenge</t>
+          <t>POOLS[5].cases[0].challenge</t>
         </is>
       </c>
     </row>
     <row r="134" ht="46" customHeight="1">
       <c r="A134" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B134" s="7" t="inlineStr">
@@ -7030,7 +7050,7 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>Used agents to map dependencies and safely decompose the engine into governed services.</t>
+          <t>Redesigned the end-to-end workflow with domain-aware agents and human review at the decision points.</t>
         </is>
       </c>
       <c r="D134" s="9" t="n"/>
@@ -7061,14 +7081,14 @@
       </c>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].action</t>
+          <t>POOLS[5].cases[0].action</t>
         </is>
       </c>
     </row>
     <row r="135" ht="46" customHeight="1">
       <c r="A135" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B135" s="7" t="inlineStr">
@@ -7078,7 +7098,7 @@
       </c>
       <c r="C135" s="8" t="inlineStr">
         <is>
-          <t>Change velocity restored without replacing the platform.</t>
+          <t>Exceptions resolved in hours rather than days.</t>
         </is>
       </c>
       <c r="D135" s="9" t="n"/>
@@ -7109,14 +7129,14 @@
       </c>
       <c r="K135" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].outcome</t>
+          <t>POOLS[5].cases[0].outcome</t>
         </is>
       </c>
     </row>
     <row r="136" ht="46" customHeight="1">
       <c r="A136" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B136" s="7" t="inlineStr">
@@ -7126,7 +7146,7 @@
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>70%</t>
         </is>
       </c>
       <c r="D136" s="9" t="n"/>
@@ -7157,14 +7177,14 @@
       </c>
       <c r="K136" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].metric.value</t>
+          <t>POOLS[5].cases[0].metric.value</t>
         </is>
       </c>
     </row>
     <row r="137" ht="46" customHeight="1">
       <c r="A137" s="7" t="inlineStr">
         <is>
-          <t>Pool 5 case 3</t>
+          <t>Pool 6 case 1</t>
         </is>
       </c>
       <c r="B137" s="7" t="inlineStr">
@@ -7174,7 +7194,7 @@
       </c>
       <c r="C137" s="8" t="inlineStr">
         <is>
-          <t>faster change cycle</t>
+          <t>touchless orders</t>
         </is>
       </c>
       <c r="D137" s="9" t="n"/>
@@ -7205,24 +7225,24 @@
       </c>
       <c r="K137" s="12" t="inlineStr">
         <is>
-          <t>POOLS[4].cases[2].metric.label</t>
+          <t>POOLS[5].cases[0].metric.label</t>
         </is>
       </c>
     </row>
     <row r="138" ht="46" customHeight="1">
       <c r="A138" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 — Process AI</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B138" s="7" t="inlineStr">
         <is>
-          <t>Eyebrow verb</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
         <is>
-          <t>TRANSFORM</t>
+          <t>Healthcare provider</t>
         </is>
       </c>
       <c r="D138" s="9" t="n"/>
@@ -7231,10 +7251,10 @@
         <v/>
       </c>
       <c r="F138" s="10" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G138" s="10" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H138" s="10" t="inlineStr">
         <is>
@@ -7243,20 +7263,24 @@
       </c>
       <c r="I138" s="11" t="inlineStr">
         <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-      <c r="J138" s="11" t="inlineStr"/>
+          <t>One line above the case title.</t>
+        </is>
+      </c>
+      <c r="J138" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K138" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].verb</t>
+          <t>POOLS[5].cases[1].client</t>
         </is>
       </c>
     </row>
     <row r="139" ht="46" customHeight="1">
       <c r="A139" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 — Process AI</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B139" s="7" t="inlineStr">
@@ -7266,7 +7290,7 @@
       </c>
       <c r="C139" s="8" t="inlineStr">
         <is>
-          <t>Process AI</t>
+          <t>Prior authorisation with people in the loop</t>
         </is>
       </c>
       <c r="D139" s="9" t="n"/>
@@ -7275,10 +7299,10 @@
         <v/>
       </c>
       <c r="F139" s="10" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G139" s="10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H139" s="10" t="inlineStr">
         <is>
@@ -7287,30 +7311,34 @@
       </c>
       <c r="I139" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-      <c r="J139" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
+        </is>
+      </c>
+      <c r="J139" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K139" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].title</t>
+          <t>POOLS[5].cases[1].title</t>
         </is>
       </c>
     </row>
     <row r="140" ht="46" customHeight="1">
       <c r="A140" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 — Process AI</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B140" s="7" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>End-to-end workflows redesigned around domain-aware agents that understand the work, not just the words. They run alongside the people who own the outcome, who stay in the loop where judgement is needed. That combination is what turns incremental savings into a step change in both efficiency and experience.</t>
+          <t>Clinical authorisation queues were growing faster than the team could staff them.</t>
         </is>
       </c>
       <c r="D140" s="9" t="n"/>
@@ -7319,10 +7347,10 @@
         <v/>
       </c>
       <c r="F140" s="10" t="n">
-        <v>58</v>
+        <v>18</v>
       </c>
       <c r="G140" s="10" t="n">
-        <v>340</v>
+        <v>110</v>
       </c>
       <c r="H140" s="10" t="inlineStr">
         <is>
@@ -7331,30 +7359,34 @@
       </c>
       <c r="I140" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-      <c r="J140" s="11" t="inlineStr"/>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
+        </is>
+      </c>
+      <c r="J140" s="11" t="inlineStr">
+        <is>
+          <t>Placeholder. No real client detail.</t>
+        </is>
+      </c>
       <c r="K140" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].description</t>
+          <t>POOLS[5].cases[1].challenge</t>
         </is>
       </c>
     </row>
     <row r="141" ht="46" customHeight="1">
       <c r="A141" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B141" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C141" s="8" t="inlineStr">
         <is>
-          <t>Consumer goods company</t>
+          <t>Agents prepared and evidenced each case; clinicians kept every approval decision.</t>
         </is>
       </c>
       <c r="D141" s="9" t="n"/>
@@ -7363,19 +7395,19 @@
         <v/>
       </c>
       <c r="F141" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G141" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H141" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I141" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J141" s="11" t="inlineStr">
@@ -7385,24 +7417,24 @@
       </c>
       <c r="K141" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].client</t>
+          <t>POOLS[5].cases[1].action</t>
         </is>
       </c>
     </row>
     <row r="142" ht="46" customHeight="1">
       <c r="A142" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B142" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>Order to cash rebuilt around agents</t>
+          <t>Clinician time moved from assembly to judgement.</t>
         </is>
       </c>
       <c r="D142" s="9" t="n"/>
@@ -7411,10 +7443,10 @@
         <v/>
       </c>
       <c r="F142" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G142" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H142" s="10" t="inlineStr">
         <is>
@@ -7423,7 +7455,7 @@
       </c>
       <c r="I142" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J142" s="11" t="inlineStr">
@@ -7433,24 +7465,24 @@
       </c>
       <c r="K142" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].title</t>
+          <t>POOLS[5].cases[1].outcome</t>
         </is>
       </c>
     </row>
     <row r="143" ht="46" customHeight="1">
       <c r="A143" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B143" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C143" s="8" t="inlineStr">
         <is>
-          <t>Order exceptions were handled manually across three shared service centres.</t>
+          <t>4x</t>
         </is>
       </c>
       <c r="D143" s="9" t="n"/>
@@ -7459,19 +7491,19 @@
         <v/>
       </c>
       <c r="F143" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G143" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H143" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I143" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J143" s="11" t="inlineStr">
@@ -7481,24 +7513,24 @@
       </c>
       <c r="K143" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].challenge</t>
+          <t>POOLS[5].cases[1].metric.value</t>
         </is>
       </c>
     </row>
     <row r="144" ht="46" customHeight="1">
       <c r="A144" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 2</t>
         </is>
       </c>
       <c r="B144" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>Redesigned the end-to-end workflow with domain-aware agents and human review at the decision points.</t>
+          <t>throughput per reviewer</t>
         </is>
       </c>
       <c r="D144" s="9" t="n"/>
@@ -7507,19 +7539,19 @@
         <v/>
       </c>
       <c r="F144" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G144" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H144" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I144" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J144" s="11" t="inlineStr">
@@ -7529,24 +7561,24 @@
       </c>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].action</t>
+          <t>POOLS[5].cases[1].metric.label</t>
         </is>
       </c>
     </row>
     <row r="145" ht="46" customHeight="1">
       <c r="A145" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B145" s="7" t="inlineStr">
         <is>
-          <t>Outcome</t>
+          <t>Client</t>
         </is>
       </c>
       <c r="C145" s="8" t="inlineStr">
         <is>
-          <t>Exceptions resolved in hours rather than days.</t>
+          <t>Logistics operator</t>
         </is>
       </c>
       <c r="D145" s="9" t="n"/>
@@ -7555,19 +7587,19 @@
         <v/>
       </c>
       <c r="F145" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G145" s="10" t="n">
-        <v>110</v>
+        <v>30</v>
       </c>
       <c r="H145" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I145" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>One line above the case title.</t>
         </is>
       </c>
       <c r="J145" s="11" t="inlineStr">
@@ -7577,24 +7609,24 @@
       </c>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].outcome</t>
+          <t>POOLS[5].cases[2].client</t>
         </is>
       </c>
     </row>
     <row r="146" ht="46" customHeight="1">
       <c r="A146" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B146" s="7" t="inlineStr">
         <is>
-          <t>Metric figure</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>Exception handling redesigned end to end</t>
         </is>
       </c>
       <c r="D146" s="9" t="n"/>
@@ -7603,19 +7635,19 @@
         <v/>
       </c>
       <c r="F146" s="10" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G146" s="10" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="H146" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I146" s="11" t="inlineStr">
         <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
+          <t>MEASURED: runs to a third line past 50 characters.</t>
         </is>
       </c>
       <c r="J146" s="11" t="inlineStr">
@@ -7625,24 +7657,24 @@
       </c>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].metric.value</t>
+          <t>POOLS[5].cases[2].title</t>
         </is>
       </c>
     </row>
     <row r="147" ht="46" customHeight="1">
       <c r="A147" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 1</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B147" s="7" t="inlineStr">
         <is>
-          <t>Metric label</t>
+          <t>Challenge</t>
         </is>
       </c>
       <c r="C147" s="8" t="inlineStr">
         <is>
-          <t>touchless orders</t>
+          <t>Freight exceptions were detected late and escalated inconsistently.</t>
         </is>
       </c>
       <c r="D147" s="9" t="n"/>
@@ -7651,19 +7683,19 @@
         <v/>
       </c>
       <c r="F147" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G147" s="10" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="H147" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I147" s="11" t="inlineStr">
         <is>
-          <t>Small caps under the figure.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J147" s="11" t="inlineStr">
@@ -7673,24 +7705,24 @@
       </c>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[0].metric.label</t>
+          <t>POOLS[5].cases[2].challenge</t>
         </is>
       </c>
     </row>
     <row r="148" ht="46" customHeight="1">
       <c r="A148" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 2</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B148" s="7" t="inlineStr">
         <is>
-          <t>Client</t>
+          <t>What we did</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>Healthcare provider</t>
+          <t>Rebuilt the workflow so agents detect, triage and brief a human on the exceptions that matter.</t>
         </is>
       </c>
       <c r="D148" s="9" t="n"/>
@@ -7699,19 +7731,19 @@
         <v/>
       </c>
       <c r="F148" s="10" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="G148" s="10" t="n">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="H148" s="10" t="inlineStr">
         <is>
-          <t>Soft</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="I148" s="11" t="inlineStr">
         <is>
-          <t>One line above the case title.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J148" s="11" t="inlineStr">
@@ -7721,24 +7753,24 @@
       </c>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[1].client</t>
+          <t>POOLS[5].cases[2].action</t>
         </is>
       </c>
     </row>
     <row r="149" ht="46" customHeight="1">
       <c r="A149" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 2</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B149" s="7" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>Outcome</t>
         </is>
       </c>
       <c r="C149" s="8" t="inlineStr">
         <is>
-          <t>Prior authorisation with people in the loop</t>
+          <t>Fewer escalations, and earlier ones.</t>
         </is>
       </c>
       <c r="D149" s="9" t="n"/>
@@ -7747,10 +7779,10 @@
         <v/>
       </c>
       <c r="F149" s="10" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="G149" s="10" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="H149" s="10" t="inlineStr">
         <is>
@@ -7759,7 +7791,7 @@
       </c>
       <c r="I149" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
+          <t>MEASURED: runs to a third line past 110 characters.</t>
         </is>
       </c>
       <c r="J149" s="11" t="inlineStr">
@@ -7769,24 +7801,24 @@
       </c>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[1].title</t>
+          <t>POOLS[5].cases[2].outcome</t>
         </is>
       </c>
     </row>
     <row r="150" ht="46" customHeight="1">
       <c r="A150" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 2</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B150" s="7" t="inlineStr">
         <is>
-          <t>Challenge</t>
+          <t>Metric figure</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>Clinical authorisation queues were growing faster than the team could staff them.</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="D150" s="9" t="n"/>
@@ -7795,19 +7827,19 @@
         <v/>
       </c>
       <c r="F150" s="10" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="G150" s="10" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="H150" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I150" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Set large. Keep it to a figure, not a sentence.</t>
         </is>
       </c>
       <c r="J150" s="11" t="inlineStr">
@@ -7817,24 +7849,24 @@
       </c>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[1].challenge</t>
+          <t>POOLS[5].cases[2].metric.value</t>
         </is>
       </c>
     </row>
     <row r="151" ht="46" customHeight="1">
       <c r="A151" s="7" t="inlineStr">
         <is>
-          <t>Pool 6 case 2</t>
+          <t>Pool 6 case 3</t>
         </is>
       </c>
       <c r="B151" s="7" t="inlineStr">
         <is>
-          <t>What we did</t>
+          <t>Metric label</t>
         </is>
       </c>
       <c r="C151" s="8" t="inlineStr">
         <is>
-          <t>Agents prepared and evidenced each case; clinicians kept every approval decision.</t>
+          <t>reduction in delay cost</t>
         </is>
       </c>
       <c r="D151" s="9" t="n"/>
@@ -7843,19 +7875,19 @@
         <v/>
       </c>
       <c r="F151" s="10" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="G151" s="10" t="n">
-        <v>115</v>
+        <v>28</v>
       </c>
       <c r="H151" s="10" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>Soft</t>
         </is>
       </c>
       <c r="I151" s="11" t="inlineStr">
         <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
+          <t>Small caps under the figure.</t>
         </is>
       </c>
       <c r="J151" s="11" t="inlineStr">
@@ -7865,1116 +7897,22 @@
       </c>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>POOLS[5].cases[1].action</t>
-        </is>
-      </c>
-    </row>
-    <row r="152" ht="46" customHeight="1">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 2</t>
-        </is>
-      </c>
-      <c r="B152" s="7" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="C152" s="8" t="inlineStr">
-        <is>
-          <t>Clinician time moved from assembly to judgement.</t>
-        </is>
-      </c>
-      <c r="D152" s="9" t="n"/>
-      <c r="E152" s="10">
-        <f>IF(D152="","",LEN(D152))</f>
-        <v/>
-      </c>
-      <c r="F152" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G152" s="10" t="n">
-        <v>110</v>
-      </c>
-      <c r="H152" s="10" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="I152" s="11" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J152" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K152" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[1].outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="153" ht="46" customHeight="1">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 2</t>
-        </is>
-      </c>
-      <c r="B153" s="7" t="inlineStr">
-        <is>
-          <t>Metric figure</t>
-        </is>
-      </c>
-      <c r="C153" s="8" t="inlineStr">
-        <is>
-          <t>4x</t>
-        </is>
-      </c>
-      <c r="D153" s="9" t="n"/>
-      <c r="E153" s="10">
-        <f>IF(D153="","",LEN(D153))</f>
-        <v/>
-      </c>
-      <c r="F153" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G153" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H153" s="10" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="I153" s="11" t="inlineStr">
-        <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J153" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K153" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[1].metric.value</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" ht="46" customHeight="1">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 2</t>
-        </is>
-      </c>
-      <c r="B154" s="7" t="inlineStr">
-        <is>
-          <t>Metric label</t>
-        </is>
-      </c>
-      <c r="C154" s="8" t="inlineStr">
-        <is>
-          <t>throughput per reviewer</t>
-        </is>
-      </c>
-      <c r="D154" s="9" t="n"/>
-      <c r="E154" s="10">
-        <f>IF(D154="","",LEN(D154))</f>
-        <v/>
-      </c>
-      <c r="F154" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G154" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="H154" s="10" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="I154" s="11" t="inlineStr">
-        <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J154" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K154" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[1].metric.label</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" ht="46" customHeight="1">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B155" s="7" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="C155" s="8" t="inlineStr">
-        <is>
-          <t>Logistics operator</t>
-        </is>
-      </c>
-      <c r="D155" s="9" t="n"/>
-      <c r="E155" s="10">
-        <f>IF(D155="","",LEN(D155))</f>
-        <v/>
-      </c>
-      <c r="F155" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G155" s="10" t="n">
-        <v>30</v>
-      </c>
-      <c r="H155" s="10" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="I155" s="11" t="inlineStr">
-        <is>
-          <t>One line above the case title.</t>
-        </is>
-      </c>
-      <c r="J155" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K155" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].client</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" ht="46" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B156" s="7" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="C156" s="8" t="inlineStr">
-        <is>
-          <t>Exception handling redesigned end to end</t>
-        </is>
-      </c>
-      <c r="D156" s="9" t="n"/>
-      <c r="E156" s="10">
-        <f>IF(D156="","",LEN(D156))</f>
-        <v/>
-      </c>
-      <c r="F156" s="10" t="n">
-        <v>8</v>
-      </c>
-      <c r="G156" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="H156" s="10" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="I156" s="11" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
-        </is>
-      </c>
-      <c r="J156" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K156" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].title</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="46" customHeight="1">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B157" s="7" t="inlineStr">
-        <is>
-          <t>Challenge</t>
-        </is>
-      </c>
-      <c r="C157" s="8" t="inlineStr">
-        <is>
-          <t>Freight exceptions were detected late and escalated inconsistently.</t>
-        </is>
-      </c>
-      <c r="D157" s="9" t="n"/>
-      <c r="E157" s="10">
-        <f>IF(D157="","",LEN(D157))</f>
-        <v/>
-      </c>
-      <c r="F157" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G157" s="10" t="n">
-        <v>110</v>
-      </c>
-      <c r="H157" s="10" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="I157" s="11" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J157" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K157" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].challenge</t>
-        </is>
-      </c>
-    </row>
-    <row r="158" ht="46" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B158" s="7" t="inlineStr">
-        <is>
-          <t>What we did</t>
-        </is>
-      </c>
-      <c r="C158" s="8" t="inlineStr">
-        <is>
-          <t>Rebuilt the workflow so agents detect, triage and brief a human on the exceptions that matter.</t>
-        </is>
-      </c>
-      <c r="D158" s="9" t="n"/>
-      <c r="E158" s="10">
-        <f>IF(D158="","",LEN(D158))</f>
-        <v/>
-      </c>
-      <c r="F158" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G158" s="10" t="n">
-        <v>115</v>
-      </c>
-      <c r="H158" s="10" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="I158" s="11" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J158" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K158" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].action</t>
-        </is>
-      </c>
-    </row>
-    <row r="159" ht="46" customHeight="1">
-      <c r="A159" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B159" s="7" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="C159" s="8" t="inlineStr">
-        <is>
-          <t>Fewer escalations, and earlier ones.</t>
-        </is>
-      </c>
-      <c r="D159" s="9" t="n"/>
-      <c r="E159" s="10">
-        <f>IF(D159="","",LEN(D159))</f>
-        <v/>
-      </c>
-      <c r="F159" s="10" t="n">
-        <v>18</v>
-      </c>
-      <c r="G159" s="10" t="n">
-        <v>110</v>
-      </c>
-      <c r="H159" s="10" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="I159" s="11" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-      <c r="J159" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K159" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].outcome</t>
-        </is>
-      </c>
-    </row>
-    <row r="160" ht="46" customHeight="1">
-      <c r="A160" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B160" s="7" t="inlineStr">
-        <is>
-          <t>Metric figure</t>
-        </is>
-      </c>
-      <c r="C160" s="8" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="D160" s="9" t="n"/>
-      <c r="E160" s="10">
-        <f>IF(D160="","",LEN(D160))</f>
-        <v/>
-      </c>
-      <c r="F160" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G160" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="H160" s="10" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="I160" s="11" t="inlineStr">
-        <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-      <c r="J160" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K160" s="12" t="inlineStr">
-        <is>
-          <t>POOLS[5].cases[2].metric.value</t>
-        </is>
-      </c>
-    </row>
-    <row r="161" ht="46" customHeight="1">
-      <c r="A161" s="7" t="inlineStr">
-        <is>
-          <t>Pool 6 case 3</t>
-        </is>
-      </c>
-      <c r="B161" s="7" t="inlineStr">
-        <is>
-          <t>Metric label</t>
-        </is>
-      </c>
-      <c r="C161" s="8" t="inlineStr">
-        <is>
-          <t>reduction in delay cost</t>
-        </is>
-      </c>
-      <c r="D161" s="9" t="n"/>
-      <c r="E161" s="10">
-        <f>IF(D161="","",LEN(D161))</f>
-        <v/>
-      </c>
-      <c r="F161" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="G161" s="10" t="n">
-        <v>28</v>
-      </c>
-      <c r="H161" s="10" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="I161" s="11" t="inlineStr">
-        <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-      <c r="J161" s="11" t="inlineStr">
-        <is>
-          <t>Placeholder. No real client detail.</t>
-        </is>
-      </c>
-      <c r="K161" s="12" t="inlineStr">
-        <is>
           <t>POOLS[5].cases[2].metric.label</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K161"/>
-  <conditionalFormatting sqref="E2:E161">
+  <autoFilter ref="A1:K151"/>
+  <conditionalFormatting sqref="E2:E151">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>AND($D2&lt;&gt;"",LEN($D2)&gt;$G2)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D161">
+  <conditionalFormatting sqref="D2:D151">
     <cfRule type="expression" priority="2" dxfId="1">
       <formula>AND($D2&lt;&gt;"",LEN($D2)&gt;$G2,$H2="HARD")</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="9" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="13" t="inlineStr">
-        <is>
-          <t>Element</t>
-        </is>
-      </c>
-      <c r="B1" s="13" t="inlineStr">
-        <is>
-          <t>Word limit</t>
-        </is>
-      </c>
-      <c r="C1" s="13" t="inlineStr">
-        <is>
-          <t>Char limit</t>
-        </is>
-      </c>
-      <c r="D1" s="13" t="inlineStr">
-        <is>
-          <t>Limit</t>
-        </is>
-      </c>
-      <c r="E1" s="13" t="inlineStr">
-        <is>
-          <t>Where it applies</t>
-        </is>
-      </c>
-      <c r="F1" s="13" t="inlineStr">
-        <is>
-          <t>What happens past it</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="32" customHeight="1">
-      <c r="A2" s="14" t="inlineStr">
-        <is>
-          <t>Headline</t>
-        </is>
-      </c>
-      <c r="B2" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C2" s="15" t="n">
-        <v>24</v>
-      </c>
-      <c r="D2" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E2" s="16" t="inlineStr">
-        <is>
-          <t>Intro screen</t>
-        </is>
-      </c>
-      <c r="F2" s="16" t="inlineStr">
-        <is>
-          <t>Type scales down; still fits.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
-        <is>
-          <t>Sub-headline</t>
-        </is>
-      </c>
-      <c r="B3" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="C3" s="15" t="n">
-        <v>130</v>
-      </c>
-      <c r="D3" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E3" s="16" t="inlineStr">
-        <is>
-          <t>Intro and framework screens</t>
-        </is>
-      </c>
-      <c r="F3" s="16" t="inlineStr">
-        <is>
-          <t>Wraps to a third line. Layout holds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="14" t="inlineStr">
-        <is>
-          <t>Button</t>
-        </is>
-      </c>
-      <c r="B4" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C4" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="D4" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E4" s="16" t="inlineStr">
-        <is>
-          <t>Intro and framework screens</t>
-        </is>
-      </c>
-      <c r="F4" s="16" t="inlineStr">
-        <is>
-          <t>Button grows to fit the label.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>Lockup line</t>
-        </is>
-      </c>
-      <c r="B5" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C5" s="15" t="n">
-        <v>22</v>
-      </c>
-      <c r="D5" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E5" s="16" t="inlineStr">
-        <is>
-          <t>Every screen, top left</t>
-        </is>
-      </c>
-      <c r="F5" s="16" t="inlineStr">
-        <is>
-          <t>Lockup grows; keep it short beside the logo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="14" t="inlineStr">
-        <is>
-          <t>Hexagon centre L1</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>Framework overview</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>Baked into the hexagon artwork, not live text. Any change needs the artwork remade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Hexagon centre L2</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D7" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>Framework overview</t>
-        </is>
-      </c>
-      <c r="F7" s="16" t="inlineStr">
-        <is>
-          <t>Baked into the hexagon artwork, not live text. Any change needs the artwork remade.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>Headline L1</t>
-        </is>
-      </c>
-      <c r="B8" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="D8" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>Two lines by design, one per row. Longer just sets wider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Headline L2</t>
-        </is>
-      </c>
-      <c r="B9" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="15" t="n">
-        <v>26</v>
-      </c>
-      <c r="D9" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>Two lines by design, one per row. Longer just sets wider.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="14" t="inlineStr">
-        <is>
-          <t>Eyebrow verb</t>
-        </is>
-      </c>
-      <c r="B10" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C10" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="D10" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>Value pool screens (6)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>Single word above the title. Longer widens the rule beside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="14" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B11" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C11" s="15" t="n">
-        <v>32</v>
-      </c>
-      <c r="D11" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>Value pool screens (6)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: overflows the column at 38 characters. It cannot wrap.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="14" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="B12" s="15" t="n">
-        <v>57</v>
-      </c>
-      <c r="C12" s="15" t="n">
-        <v>340</v>
-      </c>
-      <c r="D12" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>Value pool screens (6)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: the buttons below drop at 384 characters. Six lines is the ceiling.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Client</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C13" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="D13" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>One line above the case title.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Challenge</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C14" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="D14" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>What we did</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C15" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="D15" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="14" t="inlineStr">
-        <is>
-          <t>Outcome</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="n">
-        <v>18</v>
-      </c>
-      <c r="C16" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="D16" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 110 characters.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="14" t="inlineStr">
-        <is>
-          <t>Metric figure</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="D17" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>Set large. Keep it to a figure, not a sentence.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="14" t="inlineStr">
-        <is>
-          <t>Metric label</t>
-        </is>
-      </c>
-      <c r="B18" s="15" t="n">
-        <v>5</v>
-      </c>
-      <c r="C18" s="15" t="n">
-        <v>28</v>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>Soft</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>Small caps under the figure.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="14" t="inlineStr">
-        <is>
-          <t>Stat figure</t>
-        </is>
-      </c>
-      <c r="B19" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C19" s="15" t="n">
-        <v>9</v>
-      </c>
-      <c r="D19" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>Cannot wrap. Past ~9 characters it collides with the stat beside it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="32" customHeight="1">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Stat label</t>
-        </is>
-      </c>
-      <c r="B20" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C20" s="15" t="n">
-        <v>40</v>
-      </c>
-      <c r="D20" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>Framework screen</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: locked to two lines. A third breaks the row baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="inlineStr">
-        <is>
-          <t>Case study title</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="n">
-        <v>7</v>
-      </c>
-      <c r="C22" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>HARD</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>Case study cards (18)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>MEASURED: runs to a third line past 50 characters.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>